--- a/input/timetable/Магистратура_Юриспруденция.xlsx
+++ b/input/timetable/Магистратура_Юриспруденция.xlsx
@@ -196,9 +196,6 @@
     <t>Директор института</t>
   </si>
   <si>
-    <t>Н.Н. Хадобина</t>
-  </si>
-  <si>
     <t>"____"_______2026 г.</t>
   </si>
   <si>
@@ -266,6 +263,9 @@
   </si>
   <si>
     <t>Правовое регулирование контрольно-надзорной деятельности органов публичной власти (лек), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Н.Н. Жадобина</t>
   </si>
 </sst>
 </file>
@@ -895,31 +895,88 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -949,27 +1006,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -979,44 +1015,17 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1036,32 +1045,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1462,7 +1462,7 @@
       <c r="D4" s="46"/>
       <c r="E4" s="46"/>
       <c r="F4" s="47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4" s="45"/>
       <c r="H4" s="46"/>
@@ -1470,7 +1470,7 @@
       <c r="J4" s="46"/>
       <c r="K4" s="46"/>
       <c r="L4" s="47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -1579,40 +1579,40 @@
       <c r="A9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
       <c r="G9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="86" t="s">
+      <c r="I9" s="78" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
+      <c r="C10" s="79" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
       <c r="F10" s="44"/>
       <c r="G10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
+      <c r="I10" s="79" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
       <c r="L10" s="44"/>
     </row>
     <row r="11" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1648,64 +1648,64 @@
       <c r="B12" s="24">
         <v>6</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="61"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="82"/>
       <c r="G12" s="23" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="24">
         <v>6</v>
       </c>
-      <c r="I12" s="59"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="61"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="82"/>
     </row>
     <row r="13" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>7</v>
       </c>
-      <c r="C13" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="64"/>
+      <c r="C13" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="85"/>
       <c r="G13" s="25"/>
       <c r="H13" s="26">
         <v>7</v>
       </c>
-      <c r="I13" s="62" t="s">
-        <v>69</v>
-      </c>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="64"/>
+      <c r="I13" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="85"/>
     </row>
     <row r="14" spans="1:12" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>8</v>
       </c>
-      <c r="C14" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="67"/>
+      <c r="C14" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="88"/>
       <c r="G14" s="27"/>
       <c r="H14" s="28">
         <v>8</v>
       </c>
-      <c r="I14" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67"/>
+      <c r="I14" s="86" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="87"/>
+      <c r="K14" s="87"/>
+      <c r="L14" s="88"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="29" t="s">
@@ -1714,64 +1714,64 @@
       <c r="B15" s="24">
         <v>6</v>
       </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="52"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="77"/>
       <c r="G15" s="29" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="24">
         <v>6</v>
       </c>
-      <c r="I15" s="50"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="52"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="77"/>
     </row>
     <row r="16" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>7</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="55"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="62"/>
       <c r="G16" s="25"/>
       <c r="H16" s="26">
         <v>7</v>
       </c>
-      <c r="I16" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="55"/>
+      <c r="I16" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="62"/>
     </row>
     <row r="17" spans="1:12" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="30"/>
       <c r="B17" s="28">
         <v>8</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="55"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="62"/>
       <c r="G17" s="30"/>
       <c r="H17" s="28">
         <v>8</v>
       </c>
-      <c r="I17" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="55"/>
+      <c r="I17" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="62"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="29" t="s">
@@ -1780,64 +1780,64 @@
       <c r="B18" s="24">
         <v>6</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="52"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="77"/>
       <c r="G18" s="29" t="s">
         <v>17</v>
       </c>
       <c r="H18" s="24">
         <v>6</v>
       </c>
-      <c r="I18" s="50"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="52"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="77"/>
     </row>
     <row r="19" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="25"/>
       <c r="B19" s="26">
         <v>7</v>
       </c>
-      <c r="C19" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="55"/>
+      <c r="C19" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="62"/>
       <c r="G19" s="25"/>
       <c r="H19" s="26">
         <v>7</v>
       </c>
-      <c r="I19" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="55"/>
+      <c r="I19" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="62"/>
     </row>
     <row r="20" spans="1:12" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="30"/>
       <c r="B20" s="28">
         <v>8</v>
       </c>
-      <c r="C20" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="58"/>
+      <c r="C20" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="68"/>
       <c r="G20" s="30"/>
       <c r="H20" s="28">
         <v>8</v>
       </c>
-      <c r="I20" s="56" t="s">
-        <v>71</v>
-      </c>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="58"/>
+      <c r="I20" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="68"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="29" t="s">
@@ -1846,64 +1846,64 @@
       <c r="B21" s="24">
         <v>6</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="70"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="71"/>
       <c r="G21" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H21" s="24">
         <v>6</v>
       </c>
-      <c r="I21" s="68"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="70"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="71"/>
     </row>
     <row r="22" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="25"/>
       <c r="B22" s="26">
         <v>7</v>
       </c>
-      <c r="C22" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="64"/>
+      <c r="C22" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="85"/>
       <c r="G22" s="25"/>
       <c r="H22" s="26">
         <v>7</v>
       </c>
-      <c r="I22" s="87" t="s">
-        <v>77</v>
-      </c>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="89"/>
+      <c r="I22" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="53"/>
     </row>
     <row r="23" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="30"/>
       <c r="B23" s="28">
         <v>8</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="55"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="62"/>
       <c r="G23" s="30"/>
       <c r="H23" s="28">
         <v>8</v>
       </c>
-      <c r="I23" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="55"/>
+      <c r="I23" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="62"/>
     </row>
     <row r="24" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="29" t="s">
@@ -1912,64 +1912,64 @@
       <c r="B24" s="24">
         <v>6</v>
       </c>
-      <c r="C24" s="74"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="76"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="74"/>
       <c r="G24" s="29" t="s">
         <v>19</v>
       </c>
       <c r="H24" s="24">
         <v>6</v>
       </c>
-      <c r="I24" s="74"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="76"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="74"/>
     </row>
     <row r="25" spans="1:12" ht="79.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="31"/>
       <c r="B25" s="26">
         <v>7</v>
       </c>
-      <c r="C25" s="77" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="79"/>
+      <c r="C25" s="89" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="91"/>
       <c r="G25" s="31"/>
       <c r="H25" s="26">
         <v>7</v>
       </c>
-      <c r="I25" s="87" t="s">
-        <v>72</v>
-      </c>
-      <c r="J25" s="88"/>
-      <c r="K25" s="88"/>
-      <c r="L25" s="89"/>
+      <c r="I25" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="53"/>
     </row>
     <row r="26" spans="1:12" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="32"/>
       <c r="B26" s="28">
         <v>8</v>
       </c>
-      <c r="C26" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="67"/>
+      <c r="C26" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="88"/>
       <c r="G26" s="32"/>
       <c r="H26" s="28">
         <v>8</v>
       </c>
-      <c r="I26" s="90" t="s">
-        <v>73</v>
-      </c>
-      <c r="J26" s="91"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="92"/>
+      <c r="I26" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="J26" s="55"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="56"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="33" t="s">
@@ -1978,86 +1978,86 @@
       <c r="B27" s="24">
         <v>2</v>
       </c>
-      <c r="C27" s="80" t="s">
+      <c r="C27" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="82"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59"/>
       <c r="G27" s="33" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="24">
         <v>2</v>
       </c>
-      <c r="I27" s="80" t="s">
+      <c r="I27" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="J27" s="81"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="82"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="59"/>
     </row>
     <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="34"/>
       <c r="B28" s="26">
         <v>3</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="62"/>
       <c r="G28" s="34"/>
       <c r="H28" s="26">
         <v>3</v>
       </c>
-      <c r="I28" s="53" t="s">
+      <c r="I28" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="J28" s="54"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="55"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="62"/>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="35"/>
       <c r="B29" s="36">
         <v>4</v>
       </c>
-      <c r="C29" s="83"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="85"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="65"/>
       <c r="G29" s="35"/>
       <c r="H29" s="36">
         <v>4</v>
       </c>
-      <c r="I29" s="83"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="84"/>
-      <c r="L29" s="85"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="65"/>
     </row>
     <row r="30" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="42"/>
       <c r="B30" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="71" t="s">
+      <c r="C30" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="50"/>
       <c r="G30" s="42"/>
       <c r="H30" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="I30" s="71" t="s">
+      <c r="I30" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="73"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="49"/>
+      <c r="L30" s="50"/>
     </row>
     <row r="31" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="32" spans="1:12" x14ac:dyDescent="0.4">
@@ -2085,42 +2085,11 @@
         <v>12</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C18:F18"/>
@@ -2132,6 +2101,37 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
   </mergeCells>
   <conditionalFormatting sqref="C9:C10">
     <cfRule type="expression" priority="4">
@@ -2240,11 +2240,11 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4" s="1"/>
       <c r="L4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -2357,41 +2357,41 @@
         <v>24</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="99" t="s">
+      <c r="C9" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
       <c r="G9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="104" t="s">
+      <c r="I9" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="104"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
     </row>
     <row r="10" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="100" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
+      <c r="C10" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
       <c r="F10" s="39"/>
       <c r="G10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="100" t="s">
-        <v>61</v>
-      </c>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100"/>
+      <c r="I10" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
       <c r="L10" s="39"/>
     </row>
     <row r="11" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2427,64 +2427,64 @@
       <c r="B12" s="24">
         <v>6</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="70"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="71"/>
       <c r="G12" s="23" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="24">
         <v>6</v>
       </c>
-      <c r="I12" s="50"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="52"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="77"/>
     </row>
     <row r="13" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>7</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="64"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="85"/>
       <c r="G13" s="25"/>
       <c r="H13" s="26">
         <v>7</v>
       </c>
-      <c r="I13" s="62" t="s">
+      <c r="I13" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="64"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="85"/>
     </row>
     <row r="14" spans="1:12" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>8</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="67"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="88"/>
       <c r="G14" s="27"/>
       <c r="H14" s="28">
         <v>8</v>
       </c>
-      <c r="I14" s="65" t="s">
+      <c r="I14" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="87"/>
+      <c r="L14" s="88"/>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="29" t="s">
@@ -2493,64 +2493,64 @@
       <c r="B15" s="24">
         <v>6</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="70"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="71"/>
       <c r="G15" s="29" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="24">
         <v>6</v>
       </c>
-      <c r="I15" s="50"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="52"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="77"/>
     </row>
     <row r="16" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>7</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="55"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="62"/>
       <c r="G16" s="25"/>
       <c r="H16" s="26">
         <v>7</v>
       </c>
-      <c r="I16" s="62" t="s">
-        <v>81</v>
-      </c>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="64"/>
+      <c r="I16" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
     </row>
     <row r="17" spans="1:12" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="30"/>
       <c r="B17" s="28">
         <v>8</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="58"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="68"/>
       <c r="G17" s="30"/>
       <c r="H17" s="28">
         <v>8</v>
       </c>
-      <c r="I17" s="65" t="s">
+      <c r="I17" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
-      <c r="L17" s="67"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="88"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="29" t="s">
@@ -2559,62 +2559,62 @@
       <c r="B18" s="24">
         <v>6</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="70"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="71"/>
       <c r="G18" s="29" t="s">
         <v>17</v>
       </c>
       <c r="H18" s="24">
         <v>6</v>
       </c>
-      <c r="I18" s="93" t="s">
+      <c r="I18" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="95"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="98"/>
+    </row>
+    <row r="19" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="25"/>
       <c r="B19" s="26">
         <v>7</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="79"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="91"/>
       <c r="G19" s="25"/>
       <c r="H19" s="26">
         <v>7</v>
       </c>
-      <c r="I19" s="96"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="98"/>
+      <c r="I19" s="99"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="101"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="30"/>
       <c r="B20" s="28">
         <v>8</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="67"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="88"/>
       <c r="G20" s="30"/>
       <c r="H20" s="28">
         <v>8</v>
       </c>
-      <c r="I20" s="101"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="103"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="104"/>
     </row>
     <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="29" t="s">
@@ -2623,62 +2623,62 @@
       <c r="B21" s="24">
         <v>6</v>
       </c>
-      <c r="C21" s="93" t="s">
+      <c r="C21" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="95"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="98"/>
       <c r="G21" s="29" t="s">
         <v>18</v>
       </c>
       <c r="H21" s="24">
         <v>6</v>
       </c>
-      <c r="I21" s="68"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="70"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="71"/>
     </row>
     <row r="22" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="25"/>
       <c r="B22" s="26">
         <v>7</v>
       </c>
-      <c r="C22" s="96"/>
-      <c r="D22" s="97"/>
-      <c r="E22" s="97"/>
-      <c r="F22" s="98"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="101"/>
       <c r="G22" s="25"/>
       <c r="H22" s="26">
         <v>7</v>
       </c>
-      <c r="I22" s="62" t="s">
+      <c r="I22" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="63"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="64"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="85"/>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="30"/>
       <c r="B23" s="28">
         <v>8</v>
       </c>
-      <c r="C23" s="101"/>
-      <c r="D23" s="102"/>
-      <c r="E23" s="102"/>
-      <c r="F23" s="103"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="104"/>
       <c r="G23" s="30"/>
       <c r="H23" s="28">
         <v>8</v>
       </c>
-      <c r="I23" s="53" t="s">
+      <c r="I23" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="55"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="62"/>
     </row>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="29" t="s">
@@ -2687,64 +2687,64 @@
       <c r="B24" s="24">
         <v>6</v>
       </c>
-      <c r="C24" s="93"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="95"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="97"/>
+      <c r="F24" s="98"/>
       <c r="G24" s="29" t="s">
         <v>19</v>
       </c>
       <c r="H24" s="24">
         <v>6</v>
       </c>
-      <c r="I24" s="74"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="76"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="74"/>
     </row>
     <row r="25" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="31"/>
       <c r="B25" s="26">
         <v>7</v>
       </c>
-      <c r="C25" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55"/>
+      <c r="C25" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="62"/>
       <c r="G25" s="31"/>
       <c r="H25" s="26">
         <v>7</v>
       </c>
-      <c r="I25" s="62" t="s">
+      <c r="I25" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="J25" s="63"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="64"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="85"/>
     </row>
     <row r="26" spans="1:12" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="32"/>
       <c r="B26" s="28">
         <v>8</v>
       </c>
-      <c r="C26" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="58"/>
+      <c r="C26" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="68"/>
       <c r="G26" s="32"/>
       <c r="H26" s="28">
         <v>8</v>
       </c>
-      <c r="I26" s="65" t="s">
+      <c r="I26" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="67"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="87"/>
+      <c r="L26" s="88"/>
     </row>
     <row r="27" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="40" t="s">
@@ -2753,74 +2753,74 @@
       <c r="B27" s="37">
         <v>2</v>
       </c>
-      <c r="C27" s="93" t="s">
+      <c r="C27" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94"/>
-      <c r="F27" s="95"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="98"/>
       <c r="G27" s="33" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="24">
         <v>2</v>
       </c>
-      <c r="I27" s="93" t="s">
+      <c r="I27" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="J27" s="94"/>
-      <c r="K27" s="94"/>
-      <c r="L27" s="95"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="98"/>
     </row>
     <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="34"/>
       <c r="B28" s="26">
         <v>3</v>
       </c>
-      <c r="C28" s="96"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="98"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="101"/>
       <c r="G28" s="34"/>
       <c r="H28" s="26">
         <v>3</v>
       </c>
-      <c r="I28" s="96"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="97"/>
-      <c r="L28" s="98"/>
+      <c r="I28" s="99"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="101"/>
     </row>
     <row r="29" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="35"/>
       <c r="B29" s="36">
         <v>4</v>
       </c>
-      <c r="C29" s="96"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="98"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="100"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="101"/>
       <c r="G29" s="35"/>
       <c r="H29" s="36">
         <v>4</v>
       </c>
-      <c r="I29" s="96"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="98"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="100"/>
+      <c r="L29" s="101"/>
     </row>
     <row r="30" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="41"/>
       <c r="B30" s="28"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="103"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="104"/>
       <c r="G30" s="38"/>
       <c r="H30" s="28"/>
-      <c r="I30" s="105"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="107"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="94"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="95"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31" s="2"/>
@@ -2863,32 +2863,24 @@
         <v>12</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C23:F23"/>
@@ -2897,19 +2889,27 @@
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 K6">

--- a/input/timetable/Магистратура_Юриспруденция.xlsx
+++ b/input/timetable/Магистратура_Юриспруденция.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="24" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="99">
   <si>
     <t>пара</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Зав. кафедрой</t>
+  </si>
+  <si>
+    <t>Преподаватель</t>
   </si>
   <si>
     <t>Направление</t>
@@ -115,6 +118,18 @@
     <t>Л.А Попова</t>
   </si>
   <si>
+    <t>Сираканян А.Р.</t>
+  </si>
+  <si>
+    <t>Чарковская Н.И.</t>
+  </si>
+  <si>
+    <t>Усольцева Н.А.</t>
+  </si>
+  <si>
+    <t>Гребнева Н.Н.</t>
+  </si>
+  <si>
     <t>102-41м</t>
   </si>
   <si>
@@ -124,6 +139,9 @@
     <t>ЭУК</t>
   </si>
   <si>
+    <t>Никулина О.В.</t>
+  </si>
+  <si>
     <t>История и методология науки (лек 16 ч)</t>
   </si>
   <si>
@@ -133,9 +151,18 @@
     <t>Ответственность должностных лиц государственных и коммерческих организаций (лек), ЭОиДОТ// Основы научных исследований в области юриспруденции (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Зорькина А.А./Попов Н.А.</t>
+  </si>
+  <si>
     <t>Ответственность должностных лиц государственных и коммерческих организаций (пр), ЭОиДОТ// Основы научных исследований в области юриспруденции (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Гребнева Н.Н./Мальцев В.В.</t>
+  </si>
+  <si>
+    <t>Ельмендеева Л.В.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> История и методология науки (пр), ЭОиДОТ//</t>
   </si>
   <si>
@@ -205,6 +232,9 @@
     <t>02.02.2026 - 04.04.2026</t>
   </si>
   <si>
+    <t>Главан А.А.</t>
+  </si>
+  <si>
     <t>Научно-исследовательский семинар (Правовое обеспечение безопасности государства и бизнеса) (лек 8 ч), ЭОиДОТ; Учебная практика, научно-исследовательская работа (получение первичных навыков научно-исследовательской работы) (24 ч), ЭОиДОТ</t>
   </si>
   <si>
@@ -223,6 +253,9 @@
     <t>Актуальные проблемы уголовного и уголовно-процессуального права (лек), ЭОиДОТ// Проблемы назначения и исполнения уголовных наказаний (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Дядькин Д.С./Алиев З.Г.</t>
+  </si>
+  <si>
     <t>Актуальные проблемы уголовного и уголовно-процессуального права (пр), ЭОиДОТ// Проблемы назначения и исполнения уголовных наказаний (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -232,6 +265,12 @@
     <t>Основы научных исследований в области частного и предпринимательского права (пр), ЭОиДОТ// Контрольно-надзорные мероприятия в предпринимательской деятельности (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Манин В.А.</t>
+  </si>
+  <si>
+    <t>Неугодников И.С.</t>
+  </si>
+  <si>
     <t>Гражданско-правовые механизмы защиты прав и интересов предпринимателей (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -241,15 +280,24 @@
     <t>Правовое регулирование закупочной деятельности (пр), ЭОиДОТ// Современные проблемы предпринимательского права (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Усольцева Н.А./Неугодников И.С.</t>
+  </si>
+  <si>
     <t>Судебные экспертизы (лек), ЭОиДОТ// ФТД: Банковское право (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Чурманова А.А./Жадобина Н.Н.</t>
+  </si>
+  <si>
     <t>Судебные экспертизы (пр), ЭОиДОТ// ФТД: Банковское право (пр), ЭОиДОТ</t>
   </si>
   <si>
     <t>Гражданско-правовые механизмы защиты прав и интересов предпринимателей((лек), ЭОиДОТ// ФТД: Банковское право (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Чарковская Н.И./Жадобина Н.Н.</t>
+  </si>
+  <si>
     <t>Защита прав предпринимателей: процессуальные аспекты (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -263,6 +311,9 @@
   </si>
   <si>
     <t>Правовое регулирование контрольно-надзорной деятельности органов публичной власти (лек), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Налбандян Е.Л.</t>
   </si>
   <si>
     <t>Н.Н. Жадобина</t>
@@ -366,7 +417,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,8 +434,14 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -464,6 +521,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -557,6 +672,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -731,6 +859,34 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -778,7 +934,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -818,28 +974,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -848,6 +1007,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="255"/>
     </xf>
@@ -857,6 +1017,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -866,26 +1027,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -895,49 +1059,159 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -946,122 +1220,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1371,7 +1540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1380,100 +1549,106 @@
     <col min="4" max="4" width="22.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A1" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="47" t="s">
+      <c r="G1" s="52"/>
+      <c r="H1" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="53" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="47" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="53" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3" s="45" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="47" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="52"/>
+      <c r="H3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="47" t="s">
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="53" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="45"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="52"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="53" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -1482,44 +1657,44 @@
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J5" s="5"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="11" t="s">
+      <c r="J6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
@@ -1533,563 +1708,690 @@
       <c r="F7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="J7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="10">
+      <c r="K7" s="13"/>
+      <c r="L7" s="10">
         <v>1</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" s="16" t="s">
+      <c r="H8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="14"/>
+      <c r="L8" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="78" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="78"/>
-      <c r="K9" s="78"/>
-      <c r="L9" s="78"/>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="H9" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="97" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="97"/>
+      <c r="L9" s="97"/>
+      <c r="M9" s="97"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="44"/>
-    </row>
-    <row r="11" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="50"/>
+      <c r="H10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="50"/>
+    </row>
+    <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
       <c r="F11" s="22"/>
-      <c r="G11" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="18" t="s">
+      <c r="G11" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="J11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="25">
+        <v>6</v>
+      </c>
+      <c r="C12" s="70"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="25">
+        <v>6</v>
+      </c>
+      <c r="J12" s="70"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="32"/>
+    </row>
+    <row r="13" spans="1:14" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>7</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="26"/>
+      <c r="I13" s="27">
+        <v>7</v>
+      </c>
+      <c r="J13" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="55" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
+        <v>8</v>
+      </c>
+      <c r="C14" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30">
+        <v>8</v>
+      </c>
+      <c r="J14" s="76" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="57" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A15" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="25">
+        <v>6</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="25">
+        <v>6</v>
+      </c>
+      <c r="J15" s="61"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="32"/>
+    </row>
+    <row r="16" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>7</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="26"/>
+      <c r="I16" s="27">
+        <v>7</v>
+      </c>
+      <c r="J16" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="66"/>
+      <c r="N16" s="55" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="33"/>
+      <c r="B17" s="30">
+        <v>8</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="33"/>
+      <c r="I17" s="30">
+        <v>8</v>
+      </c>
+      <c r="J17" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="66"/>
+      <c r="N17" s="55" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A18" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="25">
+        <v>6</v>
+      </c>
+      <c r="C18" s="61"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="25">
+        <v>6</v>
+      </c>
+      <c r="J18" s="61"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="32"/>
+    </row>
+    <row r="19" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
+        <v>7</v>
+      </c>
+      <c r="C19" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="26"/>
+      <c r="I19" s="27">
+        <v>7</v>
+      </c>
+      <c r="J19" s="64" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="55" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="33"/>
+      <c r="B20" s="30">
+        <v>8</v>
+      </c>
+      <c r="C20" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="33"/>
+      <c r="I20" s="30">
+        <v>8</v>
+      </c>
+      <c r="J20" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="57" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="25">
+        <v>6</v>
+      </c>
+      <c r="C21" s="79"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="25">
+        <v>6</v>
+      </c>
+      <c r="J21" s="79"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="81"/>
+      <c r="N21" s="32"/>
+    </row>
+    <row r="22" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
+        <v>7</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="26"/>
+      <c r="I22" s="27">
+        <v>7</v>
+      </c>
+      <c r="J22" s="98" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="99"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="100"/>
+      <c r="N22" s="55" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="33"/>
+      <c r="B23" s="30">
+        <v>8</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="33"/>
+      <c r="I23" s="30">
+        <v>8</v>
+      </c>
+      <c r="J23" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="57" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="25">
+        <v>6</v>
+      </c>
+      <c r="C24" s="85"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="25">
+        <v>6</v>
+      </c>
+      <c r="J24" s="85"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="87"/>
+      <c r="N24" s="32"/>
+    </row>
+    <row r="25" spans="1:14" ht="79.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="34"/>
+      <c r="B25" s="27">
+        <v>7</v>
+      </c>
+      <c r="C25" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="34"/>
+      <c r="I25" s="27">
+        <v>7</v>
+      </c>
+      <c r="J25" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="99"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="100"/>
+      <c r="N25" s="55" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="35"/>
+      <c r="B26" s="30">
+        <v>8</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="35"/>
+      <c r="I26" s="30">
+        <v>8</v>
+      </c>
+      <c r="J26" s="101" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="102"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="57" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="20"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="22"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A12" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="24">
-        <v>6</v>
-      </c>
-      <c r="C12" s="80"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="24">
-        <v>6</v>
-      </c>
-      <c r="I12" s="80"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="82"/>
-    </row>
-    <row r="13" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
-        <v>7</v>
-      </c>
-      <c r="C13" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26">
-        <v>7</v>
-      </c>
-      <c r="I13" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="85"/>
-    </row>
-    <row r="14" spans="1:12" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
-        <v>8</v>
-      </c>
-      <c r="C14" s="86" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="28">
-        <v>8</v>
-      </c>
-      <c r="I14" s="86" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="88"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A15" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="24">
-        <v>6</v>
-      </c>
-      <c r="C15" s="75"/>
-      <c r="D15" s="76"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="24">
-        <v>6</v>
-      </c>
-      <c r="I15" s="75"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="77"/>
-    </row>
-    <row r="16" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="26">
-        <v>7</v>
-      </c>
-      <c r="I16" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="62"/>
-    </row>
-    <row r="17" spans="1:12" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="30"/>
-      <c r="B17" s="28">
-        <v>8</v>
-      </c>
-      <c r="C17" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="28">
-        <v>8</v>
-      </c>
-      <c r="I17" s="60" t="s">
-        <v>74</v>
-      </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="62"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A18" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="24">
-        <v>6</v>
-      </c>
-      <c r="C18" s="75"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="24">
-        <v>6</v>
-      </c>
-      <c r="I18" s="75"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="77"/>
-    </row>
-    <row r="19" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
-        <v>7</v>
-      </c>
-      <c r="C19" s="60" t="s">
+      <c r="B27" s="25">
+        <v>2</v>
+      </c>
+      <c r="C27" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="25">
+        <v>2</v>
+      </c>
+      <c r="J27" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="93"/>
+      <c r="N27" s="56" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="37"/>
+      <c r="B28" s="27">
+        <v>3</v>
+      </c>
+      <c r="C28" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="37"/>
+      <c r="I28" s="27">
+        <v>3</v>
+      </c>
+      <c r="J28" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="55" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="38"/>
+      <c r="B29" s="39">
+        <v>4</v>
+      </c>
+      <c r="C29" s="94"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39">
+        <v>4</v>
+      </c>
+      <c r="J29" s="94"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="40"/>
+    </row>
+    <row r="30" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="48"/>
+      <c r="B30" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="82" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="48"/>
+      <c r="I30" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" s="82" t="s">
+        <v>40</v>
+      </c>
+      <c r="K30" s="83"/>
+      <c r="L30" s="83"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="54" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B32" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26">
-        <v>7</v>
-      </c>
-      <c r="I19" s="60" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="62"/>
-    </row>
-    <row r="20" spans="1:12" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="30"/>
-      <c r="B20" s="28">
-        <v>8</v>
-      </c>
-      <c r="C20" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="28">
-        <v>8</v>
-      </c>
-      <c r="I20" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="68"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A21" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="24">
-        <v>6</v>
-      </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="24">
-        <v>6</v>
-      </c>
-      <c r="I21" s="69"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
-      <c r="L21" s="71"/>
-    </row>
-    <row r="22" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
-        <v>7</v>
-      </c>
-      <c r="C22" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26">
-        <v>7</v>
-      </c>
-      <c r="I22" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="J22" s="52"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="53"/>
-    </row>
-    <row r="23" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="30"/>
-      <c r="B23" s="28">
-        <v>8</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="28">
-        <v>8</v>
-      </c>
-      <c r="I23" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="62"/>
-    </row>
-    <row r="24" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="24">
-        <v>6</v>
-      </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="24">
-        <v>6</v>
-      </c>
-      <c r="I24" s="72"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="73"/>
-      <c r="L24" s="74"/>
-    </row>
-    <row r="25" spans="1:12" ht="79.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="31"/>
-      <c r="B25" s="26">
-        <v>7</v>
-      </c>
-      <c r="C25" s="89" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="26">
-        <v>7</v>
-      </c>
-      <c r="I25" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="52"/>
-      <c r="K25" s="52"/>
-      <c r="L25" s="53"/>
-    </row>
-    <row r="26" spans="1:12" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="32"/>
-      <c r="B26" s="28">
-        <v>8</v>
-      </c>
-      <c r="C26" s="86" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="28">
-        <v>8</v>
-      </c>
-      <c r="I26" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="56"/>
-    </row>
-    <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="24">
-        <v>2</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="24">
-        <v>2</v>
-      </c>
-      <c r="I27" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="59"/>
-    </row>
-    <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26">
-        <v>3</v>
-      </c>
-      <c r="C28" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="26">
-        <v>3</v>
-      </c>
-      <c r="I28" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="62"/>
-    </row>
-    <row r="29" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="35"/>
-      <c r="B29" s="36">
-        <v>4</v>
-      </c>
-      <c r="C29" s="63"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="36">
-        <v>4</v>
-      </c>
-      <c r="I29" s="63"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="65"/>
-    </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="42"/>
-      <c r="B30" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="50"/>
-    </row>
-    <row r="31" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B32" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>81</v>
+      <c r="L33" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C18:F18"/>
@@ -2101,59 +2403,28 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
   </mergeCells>
   <conditionalFormatting sqref="C9:C10">
     <cfRule type="expression" priority="4">
       <formula>IF(#REF!=0,"",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9">
+  <conditionalFormatting sqref="J9">
     <cfRule type="expression" priority="3">
       <formula>IF(#REF!=0,"",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10">
+  <conditionalFormatting sqref="J10">
     <cfRule type="expression" priority="1">
       <formula>IF(#REF!=0,"",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7 I7"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 K6">
+    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7 J7"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 L6">
       <formula1>"осенний, весенний"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 J6">
       <formula1>"2025-2026"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2164,7 +2435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -2172,16 +2443,18 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20" style="2" customWidth="1"/>
-    <col min="10" max="11" width="16.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <col min="11" max="12" width="16.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2190,16 +2463,17 @@
       <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2208,14 +2482,15 @@
       <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -2226,28 +2501,30 @@
       <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="L4" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+        <v>67</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="1"/>
+      <c r="M4" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -2256,45 +2533,47 @@
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2"/>
+      <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J5" s="5"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="2"/>
+      <c r="H6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="11" t="s">
+      <c r="J6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
@@ -2309,546 +2588,628 @@
       <c r="F7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="2"/>
+      <c r="H7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="J7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="10">
+      <c r="K7" s="13"/>
+      <c r="L7" s="10">
         <v>2</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="16" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="14"/>
+      <c r="L8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="107" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="105" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-    </row>
-    <row r="10" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C9" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="115"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+    </row>
+    <row r="10" spans="1:14" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="106" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="106" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="39"/>
-    </row>
-    <row r="11" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C10" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="43"/>
+    </row>
+    <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="21"/>
       <c r="F11" s="22"/>
-      <c r="G11" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="18" t="s">
+      <c r="G11" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="J11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="25">
+        <v>6</v>
+      </c>
+      <c r="C12" s="79"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="25">
+        <v>6</v>
+      </c>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="32"/>
+    </row>
+    <row r="13" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>7</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="26"/>
+      <c r="I13" s="27">
+        <v>7</v>
+      </c>
+      <c r="J13" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
+        <v>8</v>
+      </c>
+      <c r="C14" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30">
+        <v>8</v>
+      </c>
+      <c r="J14" s="76" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="57" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="25">
+        <v>6</v>
+      </c>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="25">
+        <v>6</v>
+      </c>
+      <c r="J15" s="61"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="32"/>
+    </row>
+    <row r="16" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>7</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="26"/>
+      <c r="I16" s="27">
+        <v>7</v>
+      </c>
+      <c r="J16" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="K16" s="74"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="55" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="33"/>
+      <c r="B17" s="30">
+        <v>8</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="33"/>
+      <c r="I17" s="30">
+        <v>8</v>
+      </c>
+      <c r="J17" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="57" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A18" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="25">
+        <v>6</v>
+      </c>
+      <c r="C18" s="79"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="25">
+        <v>6</v>
+      </c>
+      <c r="J18" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="105"/>
+      <c r="L18" s="105"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="32"/>
+    </row>
+    <row r="19" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
+        <v>7</v>
+      </c>
+      <c r="C19" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="26"/>
+      <c r="I19" s="27">
+        <v>7</v>
+      </c>
+      <c r="J19" s="107"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="109"/>
+      <c r="N19" s="28"/>
+    </row>
+    <row r="20" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="33"/>
+      <c r="B20" s="30">
+        <v>8</v>
+      </c>
+      <c r="C20" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" s="33"/>
+      <c r="I20" s="30">
+        <v>8</v>
+      </c>
+      <c r="J20" s="112"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="46"/>
+    </row>
+    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="25">
+        <v>6</v>
+      </c>
+      <c r="C21" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="25">
+        <v>6</v>
+      </c>
+      <c r="J21" s="79"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="81"/>
+      <c r="N21" s="32"/>
+    </row>
+    <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
+        <v>7</v>
+      </c>
+      <c r="C22" s="107"/>
+      <c r="D22" s="108"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="27">
+        <v>7</v>
+      </c>
+      <c r="J22" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="33"/>
+      <c r="B23" s="30">
+        <v>8</v>
+      </c>
+      <c r="C23" s="112"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="114"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="30">
+        <v>8</v>
+      </c>
+      <c r="J23" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="57" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="25">
+        <v>6</v>
+      </c>
+      <c r="C24" s="104"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="25">
+        <v>6</v>
+      </c>
+      <c r="J24" s="85"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="87"/>
+      <c r="N24" s="32"/>
+    </row>
+    <row r="25" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="34"/>
+      <c r="B25" s="27">
+        <v>7</v>
+      </c>
+      <c r="C25" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="34"/>
+      <c r="I25" s="27">
+        <v>7</v>
+      </c>
+      <c r="J25" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="K25" s="74"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="55" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="35"/>
+      <c r="B26" s="30">
+        <v>8</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="35"/>
+      <c r="I26" s="30">
+        <v>8</v>
+      </c>
+      <c r="J26" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="K26" s="77"/>
+      <c r="L26" s="77"/>
+      <c r="M26" s="78"/>
+      <c r="N26" s="57" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="20"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="22"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A12" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="24">
-        <v>6</v>
-      </c>
-      <c r="C12" s="69"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="24">
-        <v>6</v>
-      </c>
-      <c r="I12" s="75"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="77"/>
-    </row>
-    <row r="13" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
-        <v>7</v>
-      </c>
-      <c r="C13" s="83" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26">
-        <v>7</v>
-      </c>
-      <c r="I13" s="83" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="85"/>
-    </row>
-    <row r="14" spans="1:12" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
-        <v>8</v>
-      </c>
-      <c r="C14" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="28">
-        <v>8</v>
-      </c>
-      <c r="I14" s="86" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="88"/>
-    </row>
-    <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="24">
-        <v>6</v>
-      </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="24">
-        <v>6</v>
-      </c>
-      <c r="I15" s="75"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="77"/>
-    </row>
-    <row r="16" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="26">
-        <v>7</v>
-      </c>
-      <c r="I16" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" s="84"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="85"/>
-    </row>
-    <row r="17" spans="1:12" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="30"/>
-      <c r="B17" s="28">
-        <v>8</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="28">
-        <v>8</v>
-      </c>
-      <c r="I17" s="86" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" s="87"/>
-      <c r="K17" s="87"/>
-      <c r="L17" s="88"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A18" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="24">
-        <v>6</v>
-      </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="24">
-        <v>6</v>
-      </c>
-      <c r="I18" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="98"/>
-    </row>
-    <row r="19" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
-        <v>7</v>
-      </c>
-      <c r="C19" s="89" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26">
-        <v>7</v>
-      </c>
-      <c r="I19" s="99"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="101"/>
-    </row>
-    <row r="20" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="30"/>
-      <c r="B20" s="28">
-        <v>8</v>
-      </c>
-      <c r="C20" s="86" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="28">
-        <v>8</v>
-      </c>
-      <c r="I20" s="102"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
-      <c r="L20" s="104"/>
-    </row>
-    <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="24">
-        <v>6</v>
-      </c>
-      <c r="C21" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="97"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="24">
-        <v>6</v>
-      </c>
-      <c r="I21" s="69"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
-      <c r="L21" s="71"/>
-    </row>
-    <row r="22" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
-        <v>7</v>
-      </c>
-      <c r="C22" s="99"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26">
-        <v>7</v>
-      </c>
-      <c r="I22" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="85"/>
-    </row>
-    <row r="23" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="30"/>
-      <c r="B23" s="28">
-        <v>8</v>
-      </c>
-      <c r="C23" s="102"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="28">
-        <v>8</v>
-      </c>
-      <c r="I23" s="60" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="62"/>
-    </row>
-    <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="24">
-        <v>6</v>
-      </c>
-      <c r="C24" s="96"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="24">
-        <v>6</v>
-      </c>
-      <c r="I24" s="72"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="73"/>
-      <c r="L24" s="74"/>
-    </row>
-    <row r="25" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="31"/>
-      <c r="B25" s="26">
-        <v>7</v>
-      </c>
-      <c r="C25" s="60" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="26">
-        <v>7</v>
-      </c>
-      <c r="I25" s="83" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="84"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="85"/>
-    </row>
-    <row r="26" spans="1:12" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="32"/>
-      <c r="B26" s="28">
-        <v>8</v>
-      </c>
-      <c r="C26" s="66" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="28">
-        <v>8</v>
-      </c>
-      <c r="I26" s="86" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="88"/>
-    </row>
-    <row r="27" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="37">
+      <c r="B27" s="41">
         <v>2</v>
       </c>
-      <c r="C27" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="24">
+      <c r="C27" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="25">
         <v>2</v>
       </c>
-      <c r="I27" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="J27" s="97"/>
-      <c r="K27" s="97"/>
-      <c r="L27" s="98"/>
-    </row>
-    <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26">
+      <c r="J27" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="K27" s="105"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="106"/>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="37"/>
+      <c r="B28" s="27">
         <v>3</v>
       </c>
-      <c r="C28" s="99"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="26">
+      <c r="C28" s="107"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="27">
         <v>3</v>
       </c>
-      <c r="I28" s="99"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="101"/>
-    </row>
-    <row r="29" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="35"/>
-      <c r="B29" s="36">
+      <c r="J28" s="107"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="109"/>
+      <c r="N28" s="28"/>
+    </row>
+    <row r="29" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="38"/>
+      <c r="B29" s="39">
         <v>4</v>
       </c>
-      <c r="C29" s="99"/>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="36">
+      <c r="C29" s="107"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39">
         <v>4</v>
       </c>
-      <c r="I29" s="99"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="101"/>
-    </row>
-    <row r="30" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="41"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="104"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="94"/>
-      <c r="L30" s="95"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J29" s="107"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="109"/>
+      <c r="N29" s="40"/>
+    </row>
+    <row r="30" spans="1:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="45"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="112"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="116"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="118"/>
+      <c r="N30" s="46"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F32" s="2"/>
-      <c r="H32" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="G32" s="2"/>
+      <c r="I32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
         <v>12</v>
@@ -2856,18 +3217,53 @@
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F33" s="2"/>
-      <c r="H33" s="2" t="s">
+      <c r="G33" s="2"/>
+      <c r="I33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>81</v>
+      <c r="L33" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
@@ -2876,47 +3272,13 @@
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 K6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 L6">
       <formula1>"осенний, весенний"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7 I7"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6">
+    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7 J7"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 J6">
       <formula1>"2025-2026"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2937,14 +3299,14 @@
             <xm:f>IF('1 курс'!#REF!=0,"",'1 курс'!#REF!)</xm:f>
             <x14:dxf/>
           </x14:cfRule>
-          <xm:sqref>I9</xm:sqref>
+          <xm:sqref>J9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="1" id="{124B7ED3-990B-46F2-BCA0-8DDFDB4A8423}">
             <xm:f>IF('1 курс'!#REF!=0,"",'1 курс'!#REF!)</xm:f>
             <x14:dxf/>
           </x14:cfRule>
-          <xm:sqref>I10</xm:sqref>
+          <xm:sqref>J10</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
